--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:36</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:31</t>
+    <t xml:space="preserve">2026-09-27 23:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2024</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.16</v>
+        <v>71.57</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2024</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>2.52</v>
+        <v>25.22</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2024</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.47</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2024</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0.52</v>
+        <v>5.24</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2024</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.81</v>
+        <v>-8.07</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2024</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1.02</v>
+        <v>-10.23</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2024</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1.78</v>
+        <v>-17.78</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2024</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.14</v>
+        <v>-21.44</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2024</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3.77</v>
+        <v>-37.75</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:13</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2024_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:21</t>
+    <t xml:space="preserve">2026-10-05 08:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
